--- a/products/isolation_bearing_embedded_parts/excel_template.xlsx
+++ b/products/isolation_bearing_embedded_parts/excel_template.xlsx
@@ -541,13 +541,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,6 +580,51 @@
           <t>生产日期</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>锚筋直径(mm)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>锚筋长度(mm)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>锚筋数量倍数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>套筒外径(mm)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>套筒长度(mm)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>钢板边长(mm)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>钢板厚度(mm)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>钢筋牌号</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>钢板牌号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,6 +645,15 @@
           <t>2026年5月</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -611,6 +674,15 @@
           <t>2026年5月</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -631,6 +703,15 @@
           <t>2026年5月</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -643,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -684,6 +765,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. 锚筋直径/长度、套筒尺寸、钢板边长/厚度等参数可直接填写；留空则按标准表自动带出。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
